--- a/data/00_grape_db_versions_readme.xlsx
+++ b/data/00_grape_db_versions_readme.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dongyan.zhao/PycharmProjects/BI/grape_dartag_00_microhaplotype_db/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049C2187-B290-BB46-AD99-C117F752167D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711F7B61-EF45-0746-9BF3-93B23D65FE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7680" yWindow="1200" windowWidth="24300" windowHeight="17840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="260" yWindow="1140" windowWidth="24300" windowHeight="17840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="readme!" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
   <si>
     <t>Version</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>DG26-11432</t>
+  </si>
+  <si>
+    <t>Unique paralogous count</t>
   </si>
 </sst>
 </file>
@@ -719,7 +722,60 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1270,17 +1326,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{647F6ACF-BFC1-2544-8700-745E46D21FE7}" name="Table2" displayName="Table2" ref="A1:I23" headerRowCount="0" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18">
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{1C488C7E-C99B-F64E-B509-A88D90A95E58}" name="Version" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{2822A429-7155-DA41-BD9D-505D63066032}" name="DArT_project" headerRowDxfId="15" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{5E31B269-5D3A-834F-A927-3F644BBCC05D}" name="PI" headerRowDxfId="13" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{7EBC638E-A2B1-054B-AD6E-E36691F98C46}" name="Plates" headerRowDxfId="11" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{D2ED595B-168B-7E41-8E69-4E8DF67D0EA2}" name="Add haplotypes" headerRowDxfId="9" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{4247AA58-962C-604D-839B-CA5C26F17F30}" name="Total_count" headerRowDxfId="7" dataDxfId="6" dataCellStyle="Comma"/>
-    <tableColumn id="8" xr3:uid="{616A3294-7289-0D40-9045-CB2516B501E8}" name="Note" headerRowDxfId="5" dataDxfId="4" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{3EC8E26A-A04D-F342-A2BF-CB8849D2D528}" name="Processed by" headerRowDxfId="3" dataDxfId="2" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{07D63648-DFC3-CD43-8390-E4002D2C5493}" name="Process_date" headerRowDxfId="1" dataDxfId="0" dataCellStyle="Comma"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{647F6ACF-BFC1-2544-8700-745E46D21FE7}" name="Table2" displayName="Table2" ref="A1:J23" headerRowCount="0" totalsRowShown="0" headerRowDxfId="23" dataDxfId="21" headerRowBorderDxfId="22" tableBorderDxfId="20">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{1C488C7E-C99B-F64E-B509-A88D90A95E58}" name="Version" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{2822A429-7155-DA41-BD9D-505D63066032}" name="DArT_project" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{5E31B269-5D3A-834F-A927-3F644BBCC05D}" name="PI" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{7EBC638E-A2B1-054B-AD6E-E36691F98C46}" name="Plates" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{D2ED595B-168B-7E41-8E69-4E8DF67D0EA2}" name="Add haplotypes" headerRowDxfId="11" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{4247AA58-962C-604D-839B-CA5C26F17F30}" name="Total_count" headerRowDxfId="9" dataDxfId="8" dataCellStyle="Comma"/>
+    <tableColumn id="7" xr3:uid="{B6F0F80C-9F42-E14A-A321-A9C104DC782A}" name="Column1" headerRowDxfId="1" dataDxfId="0" dataCellStyle="Comma"/>
+    <tableColumn id="8" xr3:uid="{616A3294-7289-0D40-9045-CB2516B501E8}" name="Note" headerRowDxfId="7" dataDxfId="6" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{3EC8E26A-A04D-F342-A2BF-CB8849D2D528}" name="Processed by" headerRowDxfId="5" dataDxfId="4" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{07D63648-DFC3-CD43-8390-E4002D2C5493}" name="Process_date" headerRowDxfId="3" dataDxfId="2" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1603,7 +1660,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11F2982-5561-E34B-9B19-EDF0365F0FA7}">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.6640625" style="3" customWidth="1"/>
@@ -1611,14 +1668,14 @@
     <col min="3" max="3" width="19" style="3" customWidth="1"/>
     <col min="4" max="4" width="8.5" style="3" customWidth="1"/>
     <col min="5" max="5" width="32.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.1640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="18.1640625" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="3"/>
+    <col min="6" max="7" width="13.1640625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="30.33203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="18.1640625" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1638,16 +1695,19 @@
         <v>7</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1666,17 +1726,20 @@
       <c r="F2" s="1">
         <v>6048</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="4">
+      <c r="J2" s="4">
         <v>45909</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1695,17 +1758,20 @@
       <c r="F3" s="1">
         <v>15590</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1">
+        <v>967</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="4">
+      <c r="J3" s="4">
         <v>46036</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1724,17 +1790,20 @@
       <c r="F4" s="1">
         <v>20536</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1">
+        <v>1661</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="4">
+      <c r="J4" s="4">
         <v>46036</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>19</v>
       </c>
@@ -1753,17 +1822,18 @@
       <c r="F5" s="8">
         <v>63864</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="4">
+      <c r="J5" s="4">
         <v>46050</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>26</v>
       </c>
@@ -1782,17 +1852,18 @@
       <c r="F6" s="8">
         <v>65865</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="8"/>
+      <c r="H6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="9">
+      <c r="J6" s="9">
         <v>46090</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
@@ -1811,243 +1882,282 @@
       <c r="F7" s="1">
         <v>67886</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="1"/>
+      <c r="H7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="I7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>46160</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I8" s="1"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I9" s="1"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I10" s="1"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I11" s="1"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I12" s="1"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I13" s="1"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I14" s="1"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I15" s="1"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I16" s="1"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I17" s="1"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I18" s="1"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I19" s="1"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I20" s="1"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I21" s="1"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I22" s="1"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I23" s="1"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I24" s="1"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I25" s="1"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I26" s="1"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I27" s="1"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I28" s="1"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I29" s="1"/>
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I30" s="1"/>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I31" s="1"/>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I32" s="1"/>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I33" s="1"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I34" s="1"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I35" s="1"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I36" s="1"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="2"/>
-    </row>
-    <row r="38" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I37" s="1"/>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="2"/>
-    </row>
-    <row r="39" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I38" s="1"/>
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="2"/>
-    </row>
-    <row r="40" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I39" s="1"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="2"/>
-    </row>
-    <row r="41" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I40" s="1"/>
+      <c r="J40" s="2"/>
+    </row>
+    <row r="41" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I41" s="1"/>
+      <c r="J41" s="2"/>
+    </row>
+    <row r="42" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I42" s="1"/>
+      <c r="J42" s="2"/>
+    </row>
+    <row r="43" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I43" s="1"/>
+      <c r="J43" s="2"/>
+    </row>
+    <row r="44" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="2"/>
-    </row>
-    <row r="45" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="I44" s="1"/>
+      <c r="J44" s="2"/>
+    </row>
+    <row r="45" spans="6:10" x14ac:dyDescent="0.2">
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="2"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
